--- a/docs/glossary/UZI_atamalari_tekshirilgan.xlsx
+++ b/docs/glossary/UZI_atamalari_tekshirilgan.xlsx
@@ -514,6 +514,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="35.05" customHeight="1" s="13">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -526,6 +527,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="13">
       <c r="A5" s="17" t="inlineStr">
         <is>
@@ -598,6 +600,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="13">
       <c r="A12" s="15" t="inlineStr">
         <is>
@@ -714,6 +717,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="13">
       <c r="A23" s="15" t="inlineStr">
         <is>
@@ -729,7 +733,7 @@
         </is>
       </c>
       <c r="B24" s="20" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="13">
@@ -739,7 +743,7 @@
         </is>
       </c>
       <c r="B25" s="20" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="13">
@@ -749,7 +753,7 @@
         </is>
       </c>
       <c r="B26" s="20" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="13">
@@ -769,7 +773,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="13">
@@ -782,13 +786,14 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Tekshiruv natijasi</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Barcha 227 mavjud atama ko‘rib chiqildi; 55 ta atamada tarjima yoki tibbiy izoh aniqlashtirildi.</t>
         </is>
@@ -807,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J228"/>
+  <dimension ref="A1:J229"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="12" min="1" max="1"/>
@@ -3550,7 +3555,7 @@
       </c>
       <c r="H64" s="24" t="inlineStr">
         <is>
-          <t>siljish to‘lqini elastografiyasi (SWE)</t>
+          <t>to‘lqin siljish elastografiyasi (SWE)</t>
         </is>
       </c>
       <c r="I64" s="24" t="inlineStr">
@@ -3587,10 +3592,14 @@
       <c r="F65" s="23" t="n"/>
       <c r="G65" s="24" t="inlineStr">
         <is>
-          <t>To'g'ri</t>
-        </is>
-      </c>
-      <c r="H65" s="24" t="n"/>
+          <t>Tuzatildi</t>
+        </is>
+      </c>
+      <c r="H65" s="24" t="inlineStr">
+        <is>
+          <t>to‘lqin siljish elastografiyasi (SWE)</t>
+        </is>
+      </c>
       <c r="I65" s="24" t="n"/>
       <c r="J65" s="24" t="inlineStr">
         <is>
@@ -9975,6 +9984,44 @@
       <c r="H228" s="24" t="n"/>
       <c r="I228" s="24" t="n"/>
       <c r="J228" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="22" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="23" t="inlineStr">
+        <is>
+          <t>Tasvir va exogenlik</t>
+        </is>
+      </c>
+      <c r="C229" s="23" t="inlineStr">
+        <is>
+          <t>imaging</t>
+        </is>
+      </c>
+      <c r="D229" s="23" t="n"/>
+      <c r="E229" s="23" t="inlineStr">
+        <is>
+          <t>tasvir</t>
+        </is>
+      </c>
+      <c r="F229" s="23" t="inlineStr">
+        <is>
+          <t>Ultratovush yordamida olingan tasvir yoki tasvir olish jarayoni (masalan, "elastography imaging" — elastografiya tasviri).</t>
+        </is>
+      </c>
+      <c r="G229" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H229" s="24" t="n"/>
+      <c r="I229" s="24" t="n"/>
+      <c r="J229" s="24" t="inlineStr">
         <is>
           <t>Yo'q</t>
         </is>

--- a/docs/glossary/UZI_atamalari_tekshirilgan.xlsx
+++ b/docs/glossary/UZI_atamalari_tekshirilgan.xlsx
@@ -514,7 +514,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="35.05" customHeight="1" s="13">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -527,7 +526,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="13">
       <c r="A5" s="17" t="inlineStr">
         <is>
@@ -600,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="13">
       <c r="A12" s="15" t="inlineStr">
         <is>
@@ -717,7 +714,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="13">
       <c r="A23" s="15" t="inlineStr">
         <is>
@@ -786,7 +782,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
@@ -812,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J229"/>
+  <dimension ref="A1:J245"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="12" min="1" max="1"/>
@@ -10022,6 +10017,582 @@
       <c r="H229" s="24" t="n"/>
       <c r="I229" s="24" t="n"/>
       <c r="J229" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="22" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="23" t="inlineStr">
+        <is>
+          <t>Qorin bo'shlig'i a'zolari</t>
+        </is>
+      </c>
+      <c r="C230" s="23" t="inlineStr">
+        <is>
+          <t>interstitial edematous pancreatitis</t>
+        </is>
+      </c>
+      <c r="D230" s="23" t="inlineStr">
+        <is>
+          <t>interstitial oedematous pancreatitis; edematous pancreatitis</t>
+        </is>
+      </c>
+      <c r="E230" s="23" t="inlineStr">
+        <is>
+          <t>interstitsial (shishli) pankreatit</t>
+        </is>
+      </c>
+      <c r="F230" s="23" t="n"/>
+      <c r="G230" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H230" s="24" t="n"/>
+      <c r="I230" s="24" t="n"/>
+      <c r="J230" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="22" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="23" t="inlineStr">
+        <is>
+          <t>Qorin bo'shlig'i a'zolari</t>
+        </is>
+      </c>
+      <c r="C231" s="23" t="inlineStr">
+        <is>
+          <t>necrotizing pancreatitis</t>
+        </is>
+      </c>
+      <c r="D231" s="23" t="inlineStr">
+        <is>
+          <t>necrotising pancreatitis</t>
+        </is>
+      </c>
+      <c r="E231" s="23" t="inlineStr">
+        <is>
+          <t>nekrotik pankreatit</t>
+        </is>
+      </c>
+      <c r="F231" s="23" t="n"/>
+      <c r="G231" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H231" s="24" t="n"/>
+      <c r="I231" s="24" t="n"/>
+      <c r="J231" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="22" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="23" t="inlineStr">
+        <is>
+          <t>Qorin bo'shlig'i a'zolari</t>
+        </is>
+      </c>
+      <c r="C232" s="23" t="inlineStr">
+        <is>
+          <t>peripancreatic fluid</t>
+        </is>
+      </c>
+      <c r="D232" s="23" t="n"/>
+      <c r="E232" s="23" t="inlineStr">
+        <is>
+          <t>bez atrofidagi suyuqlik</t>
+        </is>
+      </c>
+      <c r="F232" s="23" t="n"/>
+      <c r="G232" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H232" s="24" t="n"/>
+      <c r="I232" s="24" t="n"/>
+      <c r="J232" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="22" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C233" s="23" t="inlineStr">
+        <is>
+          <t>fluid collection</t>
+        </is>
+      </c>
+      <c r="D233" s="23" t="n"/>
+      <c r="E233" s="23" t="inlineStr">
+        <is>
+          <t>suyuqlik to'plami</t>
+        </is>
+      </c>
+      <c r="F233" s="23" t="n"/>
+      <c r="G233" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H233" s="24" t="n"/>
+      <c r="I233" s="24" t="n"/>
+      <c r="J233" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="22" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="23" t="inlineStr">
+        <is>
+          <t>Qorin bo'shlig'i a'zolari</t>
+        </is>
+      </c>
+      <c r="C234" s="23" t="inlineStr">
+        <is>
+          <t>omental bursa</t>
+        </is>
+      </c>
+      <c r="D234" s="23" t="inlineStr">
+        <is>
+          <t>lesser sac</t>
+        </is>
+      </c>
+      <c r="E234" s="23" t="inlineStr">
+        <is>
+          <t>charvi xaltasi (omental bursa)</t>
+        </is>
+      </c>
+      <c r="F234" s="23" t="n"/>
+      <c r="G234" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H234" s="24" t="n"/>
+      <c r="I234" s="24" t="n"/>
+      <c r="J234" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="22" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C235" s="23" t="inlineStr">
+        <is>
+          <t>atrophic</t>
+        </is>
+      </c>
+      <c r="D235" s="23" t="n"/>
+      <c r="E235" s="23" t="inlineStr">
+        <is>
+          <t>atrofik</t>
+        </is>
+      </c>
+      <c r="F235" s="23" t="n"/>
+      <c r="G235" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H235" s="24" t="n"/>
+      <c r="I235" s="24" t="n"/>
+      <c r="J235" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="22" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C236" s="23" t="inlineStr">
+        <is>
+          <t>pseudocyst</t>
+        </is>
+      </c>
+      <c r="D236" s="23" t="n"/>
+      <c r="E236" s="23" t="inlineStr">
+        <is>
+          <t>psevdokista</t>
+        </is>
+      </c>
+      <c r="F236" s="23" t="n"/>
+      <c r="G236" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H236" s="24" t="n"/>
+      <c r="I236" s="24" t="n"/>
+      <c r="J236" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="22" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C237" s="23" t="inlineStr">
+        <is>
+          <t>pseudoaneurysm</t>
+        </is>
+      </c>
+      <c r="D237" s="23" t="inlineStr">
+        <is>
+          <t>false aneurysm</t>
+        </is>
+      </c>
+      <c r="E237" s="23" t="inlineStr">
+        <is>
+          <t>psevdoanevrizma</t>
+        </is>
+      </c>
+      <c r="F237" s="23" t="n"/>
+      <c r="G237" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H237" s="24" t="n"/>
+      <c r="I237" s="24" t="n"/>
+      <c r="J237" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="22" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="23" t="inlineStr">
+        <is>
+          <t>Doppler</t>
+        </is>
+      </c>
+      <c r="C238" s="23" t="inlineStr">
+        <is>
+          <t>splenic artery</t>
+        </is>
+      </c>
+      <c r="D238" s="23" t="n"/>
+      <c r="E238" s="23" t="inlineStr">
+        <is>
+          <t>taloq arteriyasi</t>
+        </is>
+      </c>
+      <c r="F238" s="23" t="n"/>
+      <c r="G238" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H238" s="24" t="n"/>
+      <c r="I238" s="24" t="n"/>
+      <c r="J238" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="22" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="23" t="inlineStr">
+        <is>
+          <t>Tasvir va exogenlik</t>
+        </is>
+      </c>
+      <c r="C239" s="23" t="inlineStr">
+        <is>
+          <t>splenic window</t>
+        </is>
+      </c>
+      <c r="D239" s="23" t="n"/>
+      <c r="E239" s="23" t="inlineStr">
+        <is>
+          <t>taloq oynasi (taloq orqali kirish)</t>
+        </is>
+      </c>
+      <c r="F239" s="23" t="n"/>
+      <c r="G239" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H239" s="24" t="n"/>
+      <c r="I239" s="24" t="n"/>
+      <c r="J239" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="22" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="23" t="inlineStr">
+        <is>
+          <t>Tasvir va exogenlik</t>
+        </is>
+      </c>
+      <c r="C240" s="23" t="inlineStr">
+        <is>
+          <t>cross section</t>
+        </is>
+      </c>
+      <c r="D240" s="23" t="inlineStr">
+        <is>
+          <t>cross-section; transverse section</t>
+        </is>
+      </c>
+      <c r="E240" s="23" t="inlineStr">
+        <is>
+          <t>ko'ndalang kesim</t>
+        </is>
+      </c>
+      <c r="F240" s="23" t="n"/>
+      <c r="G240" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H240" s="24" t="n"/>
+      <c r="I240" s="24" t="n"/>
+      <c r="J240" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="22" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="23" t="inlineStr">
+        <is>
+          <t>Tasvir va exogenlik</t>
+        </is>
+      </c>
+      <c r="C241" s="23" t="inlineStr">
+        <is>
+          <t>long section</t>
+        </is>
+      </c>
+      <c r="D241" s="23" t="inlineStr">
+        <is>
+          <t>longitudinal section</t>
+        </is>
+      </c>
+      <c r="E241" s="23" t="inlineStr">
+        <is>
+          <t>bo'ylama kesim</t>
+        </is>
+      </c>
+      <c r="F241" s="23" t="n"/>
+      <c r="G241" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H241" s="24" t="n"/>
+      <c r="I241" s="24" t="n"/>
+      <c r="J241" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="22" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="23" t="inlineStr">
+        <is>
+          <t>Doppler</t>
+        </is>
+      </c>
+      <c r="C242" s="23" t="inlineStr">
+        <is>
+          <t>vascularity</t>
+        </is>
+      </c>
+      <c r="D242" s="23" t="inlineStr">
+        <is>
+          <t>vascularization; vascularisation</t>
+        </is>
+      </c>
+      <c r="E242" s="23" t="inlineStr">
+        <is>
+          <t>qon bilan ta'minlanish (vaskulyarizatsiya)</t>
+        </is>
+      </c>
+      <c r="F242" s="23" t="n"/>
+      <c r="G242" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H242" s="24" t="n"/>
+      <c r="I242" s="24" t="n"/>
+      <c r="J242" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="22" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C243" s="23" t="inlineStr">
+        <is>
+          <t>epigastric pain</t>
+        </is>
+      </c>
+      <c r="D243" s="23" t="n"/>
+      <c r="E243" s="23" t="inlineStr">
+        <is>
+          <t>epigastral og'riq</t>
+        </is>
+      </c>
+      <c r="F243" s="23" t="n"/>
+      <c r="G243" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H243" s="24" t="n"/>
+      <c r="I243" s="24" t="n"/>
+      <c r="J243" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="22" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C244" s="23" t="inlineStr">
+        <is>
+          <t>upper limit of normal</t>
+        </is>
+      </c>
+      <c r="D244" s="23" t="inlineStr">
+        <is>
+          <t>ULN</t>
+        </is>
+      </c>
+      <c r="E244" s="23" t="inlineStr">
+        <is>
+          <t>normaning yuqori chegarasi</t>
+        </is>
+      </c>
+      <c r="F244" s="23" t="n"/>
+      <c r="G244" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H244" s="24" t="n"/>
+      <c r="I244" s="24" t="n"/>
+      <c r="J244" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="22" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="23" t="inlineStr">
+        <is>
+          <t>Tasvir va exogenlik</t>
+        </is>
+      </c>
+      <c r="C245" s="23" t="inlineStr">
+        <is>
+          <t>caudally</t>
+        </is>
+      </c>
+      <c r="D245" s="23" t="n"/>
+      <c r="E245" s="23" t="inlineStr">
+        <is>
+          <t>kaudal yo'nalishda (pastga qarab)</t>
+        </is>
+      </c>
+      <c r="F245" s="23" t="n"/>
+      <c r="G245" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H245" s="24" t="n"/>
+      <c r="I245" s="24" t="n"/>
+      <c r="J245" s="24" t="inlineStr">
         <is>
           <t>Yo'q</t>
         </is>

--- a/docs/glossary/UZI_atamalari_tekshirilgan.xlsx
+++ b/docs/glossary/UZI_atamalari_tekshirilgan.xlsx
@@ -807,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J245"/>
+  <dimension ref="A1:J269"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="12" min="1" max="1"/>
@@ -965,7 +965,7 @@
       </c>
       <c r="I3" s="24" t="inlineStr">
         <is>
-          <t>Atrofdagi to‘qimaga nisbatan pastroq echogenlikka ega, ya’ni qoraroq ko‘rinadi.</t>
+          <t>Atrofdagi to‘qimaga nisbatan pastroq exogenlikka ega, ya’ni qoraroq ko‘rinadi.</t>
         </is>
       </c>
       <c r="J3" s="24" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="I4" s="24" t="inlineStr">
         <is>
-          <t>Atrofdagi to‘qimaga nisbatan echogenligi bir xil.</t>
+          <t>Atrofdagi to‘qimaga nisbatan exogenligi bir xil.</t>
         </is>
       </c>
       <c r="J4" s="24" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
-          <t>hyperechogenic; echogenic</t>
+          <t>hyperechogenic</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="I5" s="24" t="inlineStr">
         <is>
-          <t>Atrofdagi to‘qimaga nisbatan yuqoriroq echogenlikka ega, ya’ni yorqinroq ko‘rinadi.</t>
+          <t>Atrofdagi to‘qimaga nisbatan yuqoriroq exogenlikka ega, ya’ni yorqinroq ko‘rinadi.</t>
         </is>
       </c>
       <c r="J5" s="24" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>echogenlik</t>
+          <t>exogenlik</t>
         </is>
       </c>
       <c r="I6" s="24" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="I8" s="24" t="inlineStr">
         <is>
-          <t>Ichki echotuzilmasi bir xil emas, turli echogenlikdagi qismlardan iborat.</t>
+          <t>Ichki exotuzilmasi bir xil emas, turli exogenlikdagi qismlardan iborat.</t>
         </is>
       </c>
       <c r="J8" s="24" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
-          <t>Ichki echotuzilmasi bir xil yoki bir maromda ko‘rinadi.</t>
+          <t>Ichki exotuzilmasi bir xil yoki bir maromda ko‘rinadi.</t>
         </is>
       </c>
       <c r="J9" s="24" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="H10" s="24" t="inlineStr">
         <is>
-          <t>echogen o‘choq</t>
+          <t>exogen o‘choq</t>
         </is>
       </c>
       <c r="I10" s="24" t="inlineStr">
@@ -2191,11 +2191,19 @@
       </c>
       <c r="G31" s="24" t="inlineStr">
         <is>
-          <t>To'g'ri</t>
-        </is>
-      </c>
-      <c r="H31" s="24" t="n"/>
-      <c r="I31" s="24" t="n"/>
+          <t>Tuzatildi</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>chastota</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>Ultratovush to‘lqinining chastotasi (MHz). Chastota oshganda kichik tuzilmalarni ajrata olish qobiliyati yaxshilanadi, lekin ultratovush chuqurga kamroq kiradi.</t>
+        </is>
+      </c>
       <c r="J31" s="24" t="inlineStr">
         <is>
           <t>Ha</t>
@@ -2352,7 +2360,7 @@
       </c>
       <c r="H35" s="24" t="inlineStr">
         <is>
-          <t>fazoviy ajratish qobiliyati</t>
+          <t>ajrata olish qobiliyati</t>
         </is>
       </c>
       <c r="I35" s="24" t="inlineStr">
@@ -2398,7 +2406,7 @@
       </c>
       <c r="H36" s="24" t="inlineStr">
         <is>
-          <t>aksial ajratish qobiliyati</t>
+          <t>aksial ajrata olish qobiliyati</t>
         </is>
       </c>
       <c r="I36" s="24" t="inlineStr">
@@ -2444,7 +2452,7 @@
       </c>
       <c r="H37" s="24" t="inlineStr">
         <is>
-          <t>lateral ajratish qobiliyati</t>
+          <t>lateral ajrata olish qobiliyati</t>
         </is>
       </c>
       <c r="I37" s="24" t="inlineStr">
@@ -4284,7 +4292,7 @@
       </c>
       <c r="D83" s="23" t="inlineStr">
         <is>
-          <t>CBD; bile duct</t>
+          <t>CBD</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
@@ -4333,10 +4341,14 @@
       <c r="F84" s="23" t="n"/>
       <c r="G84" s="24" t="inlineStr">
         <is>
-          <t>To'g'ri</t>
-        </is>
-      </c>
-      <c r="H84" s="24" t="n"/>
+          <t>Tuzatildi</t>
+        </is>
+      </c>
+      <c r="H84" s="24" t="inlineStr">
+        <is>
+          <t>jigardagi o‘t yo‘llari</t>
+        </is>
+      </c>
       <c r="I84" s="24" t="n"/>
       <c r="J84" s="24" t="inlineStr">
         <is>
@@ -4900,7 +4912,7 @@
       </c>
       <c r="D99" s="23" t="inlineStr">
         <is>
-          <t>lymph nodes; lymphadenopathy</t>
+          <t>lymph nodes</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
@@ -4921,7 +4933,7 @@
       </c>
       <c r="I99" s="24" t="inlineStr">
         <is>
-          <t>Limfa tizimining tugunli tuzilmasi. 'Lymphadenopathy' esa limfa tugunlarining patologik kattalashishi/o‘zgarishini anglatadi.</t>
+          <t>Limfa tizimining tugunli tuzilmasi. Kattalashgani — kattalashgan limfa tuguni; patologik holat — limfadenopatiya (alohida atama).</t>
         </is>
       </c>
       <c r="J99" s="24" t="inlineStr">
@@ -4982,11 +4994,7 @@
           <t>appendix</t>
         </is>
       </c>
-      <c r="D101" s="23" t="inlineStr">
-        <is>
-          <t>appendicitis</t>
-        </is>
-      </c>
+      <c r="D101" s="23" t="n"/>
       <c r="E101" s="23" t="inlineStr">
         <is>
           <t>chuvalchangsimon o'simta (appendiks)</t>
@@ -5000,12 +5008,12 @@
       </c>
       <c r="H101" s="24" t="inlineStr">
         <is>
-          <t>chuvalchangsimon o‘simta (appendiks)</t>
+          <t>appendiks (chuvalchangsimon o‘simta)</t>
         </is>
       </c>
       <c r="I101" s="24" t="inlineStr">
         <is>
-          <t>Appendix — chuvalchangsimon o‘simta; appendicitis esa uning yallig‘lanishi.</t>
+          <t>Anatomik tuzilma. Uning yallig‘lanishi — appenditsit (alohida atama).</t>
         </is>
       </c>
       <c r="J101" s="24" t="inlineStr">
@@ -5288,7 +5296,7 @@
       </c>
       <c r="D109" s="23" t="inlineStr">
         <is>
-          <t>complex mass</t>
+          <t>complex cysts</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
@@ -5308,7 +5316,7 @@
       </c>
       <c r="H109" s="24" t="inlineStr">
         <is>
-          <t>murakkab kista</t>
+          <t>murakkab tuzilishli kista</t>
         </is>
       </c>
       <c r="I109" s="24" t="inlineStr">
@@ -5359,7 +5367,7 @@
       </c>
       <c r="I110" s="24" t="inlineStr">
         <is>
-          <t>Qon tomir kelib chiqishli, ko‘pincha xavfsiz jigar hosilasi; UZI ko‘rinishi turlicha bo‘lishi mumkin.</t>
+          <t>Qon tomir kelib chiqishli, ko‘pincha yaxshi sifatli jigar hosilasi; UZI ko‘rinishi turlicha bo‘lishi mumkin.</t>
         </is>
       </c>
       <c r="J110" s="24" t="inlineStr">
@@ -5821,11 +5829,19 @@
       <c r="F122" s="23" t="n"/>
       <c r="G122" s="24" t="inlineStr">
         <is>
-          <t>To'g'ri</t>
-        </is>
-      </c>
-      <c r="H122" s="24" t="n"/>
-      <c r="I122" s="24" t="n"/>
+          <t>Tuzatildi</t>
+        </is>
+      </c>
+      <c r="H122" s="24" t="inlineStr">
+        <is>
+          <t>yaxshi sifatli</t>
+        </is>
+      </c>
+      <c r="I122" s="24" t="inlineStr">
+        <is>
+          <t>Benign tumor — yaxshi sifatli o‘sma; benign lesion — kontekstga qarab yaxshi sifatli o‘choq yoki hosila.</t>
+        </is>
+      </c>
       <c r="J122" s="24" t="inlineStr">
         <is>
           <t>Yo'q</t>
@@ -5864,12 +5880,12 @@
       </c>
       <c r="H123" s="24" t="inlineStr">
         <is>
-          <t>xavfli (malign)</t>
+          <t>yomon sifatli</t>
         </is>
       </c>
       <c r="I123" s="24" t="inlineStr">
         <is>
-          <t>Malign — xavfli; 'malignancy' esa xavfli o‘sma/xavflilik holatini bildiradi.</t>
+          <t>Malignant — yomon sifatli; malignancy — yomon sifatli o‘sma yoki yomon sifatlilik holati.</t>
         </is>
       </c>
       <c r="J123" s="24" t="inlineStr">
@@ -8808,7 +8824,7 @@
       </c>
       <c r="D199" s="23" t="inlineStr">
         <is>
-          <t>fontanelle; fontanel</t>
+          <t>anterior fontanel</t>
         </is>
       </c>
       <c r="E199" s="23" t="inlineStr">
@@ -8828,7 +8844,7 @@
       </c>
       <c r="H199" s="24" t="inlineStr">
         <is>
-          <t>oldingi katta liqildoq</t>
+          <t>oldingi liqildoq</t>
         </is>
       </c>
       <c r="I199" s="24" t="inlineStr">
@@ -9076,11 +9092,7 @@
           <t>germinal matrix</t>
         </is>
       </c>
-      <c r="D206" s="23" t="inlineStr">
-        <is>
-          <t>germinal matrix hemorrhage</t>
-        </is>
-      </c>
+      <c r="D206" s="23" t="n"/>
       <c r="E206" s="23" t="inlineStr">
         <is>
           <t>germinal matriks</t>
@@ -9246,12 +9258,12 @@
       </c>
       <c r="H210" s="24" t="inlineStr">
         <is>
-          <t>periventrikulyar echogenlik</t>
+          <t>periventrikulyar exogenlik</t>
         </is>
       </c>
       <c r="I210" s="24" t="inlineStr">
         <is>
-          <t>Yon qorinchalar atrofidagi miya to‘qimasining ultratovushda echogenligi; oshishi klinik kontekstda baholanadi.</t>
+          <t>Yon qorinchalar atrofidagi miya to‘qimasining ultratovushda exogenligi; oshishi klinik kontekstda baholanadi.</t>
         </is>
       </c>
       <c r="J210" s="24" t="inlineStr">
@@ -9274,11 +9286,7 @@
           <t>brain parenchyma</t>
         </is>
       </c>
-      <c r="D211" s="23" t="inlineStr">
-        <is>
-          <t>parenchyma</t>
-        </is>
-      </c>
+      <c r="D211" s="23" t="n"/>
       <c r="E211" s="23" t="inlineStr">
         <is>
           <t>miya parenximasi</t>
@@ -9960,11 +9968,7 @@
           <t>interventricular septum</t>
         </is>
       </c>
-      <c r="D228" s="23" t="inlineStr">
-        <is>
-          <t>septum</t>
-        </is>
-      </c>
+      <c r="D228" s="23" t="n"/>
       <c r="E228" s="23" t="inlineStr">
         <is>
           <t>qorinchalararo to'siq</t>
@@ -10593,6 +10597,878 @@
       <c r="H245" s="24" t="n"/>
       <c r="I245" s="24" t="n"/>
       <c r="J245" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="22" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C246" s="23" t="inlineStr">
+        <is>
+          <t>parenchyma</t>
+        </is>
+      </c>
+      <c r="D246" s="23" t="n"/>
+      <c r="E246" s="23" t="inlineStr">
+        <is>
+          <t>parenxima</t>
+        </is>
+      </c>
+      <c r="F246" s="23" t="n"/>
+      <c r="G246" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H246" s="24" t="n"/>
+      <c r="I246" s="24" t="n"/>
+      <c r="J246" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="22" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="23" t="inlineStr">
+        <is>
+          <t>Qorin bo'shlig'i a'zolari</t>
+        </is>
+      </c>
+      <c r="C247" s="23" t="inlineStr">
+        <is>
+          <t>liver parenchyma</t>
+        </is>
+      </c>
+      <c r="D247" s="23" t="n"/>
+      <c r="E247" s="23" t="inlineStr">
+        <is>
+          <t>jigar parenximasi</t>
+        </is>
+      </c>
+      <c r="F247" s="23" t="n"/>
+      <c r="G247" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H247" s="24" t="n"/>
+      <c r="I247" s="24" t="n"/>
+      <c r="J247" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="22" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="23" t="inlineStr">
+        <is>
+          <t>Qalqonsimon bez</t>
+        </is>
+      </c>
+      <c r="C248" s="23" t="inlineStr">
+        <is>
+          <t>thyroid parenchyma</t>
+        </is>
+      </c>
+      <c r="D248" s="23" t="n"/>
+      <c r="E248" s="23" t="inlineStr">
+        <is>
+          <t>qalqonsimon bez parenximasi</t>
+        </is>
+      </c>
+      <c r="F248" s="23" t="n"/>
+      <c r="G248" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H248" s="24" t="n"/>
+      <c r="I248" s="24" t="n"/>
+      <c r="J248" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="22" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="23" t="inlineStr">
+        <is>
+          <t>Qorin bo'shlig'i a'zolari</t>
+        </is>
+      </c>
+      <c r="C249" s="23" t="inlineStr">
+        <is>
+          <t>bile duct</t>
+        </is>
+      </c>
+      <c r="D249" s="23" t="inlineStr">
+        <is>
+          <t>bile ducts</t>
+        </is>
+      </c>
+      <c r="E249" s="23" t="inlineStr">
+        <is>
+          <t>o‘t yo‘li</t>
+        </is>
+      </c>
+      <c r="F249" s="23" t="n"/>
+      <c r="G249" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H249" s="24" t="n"/>
+      <c r="I249" s="24" t="n"/>
+      <c r="J249" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="22" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="23" t="inlineStr">
+        <is>
+          <t>Qorin bo'shlig'i a'zolari</t>
+        </is>
+      </c>
+      <c r="C250" s="23" t="inlineStr">
+        <is>
+          <t>extrahepatic bile duct</t>
+        </is>
+      </c>
+      <c r="D250" s="23" t="inlineStr">
+        <is>
+          <t>extrahepatic bile ducts; extrahepatic ducts</t>
+        </is>
+      </c>
+      <c r="E250" s="23" t="inlineStr">
+        <is>
+          <t>jigardan tashqari o‘t yo‘llari</t>
+        </is>
+      </c>
+      <c r="F250" s="23" t="n"/>
+      <c r="G250" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H250" s="24" t="n"/>
+      <c r="I250" s="24" t="n"/>
+      <c r="J250" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="22" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C251" s="23" t="inlineStr">
+        <is>
+          <t>lymphadenopathy</t>
+        </is>
+      </c>
+      <c r="D251" s="23" t="n"/>
+      <c r="E251" s="23" t="inlineStr">
+        <is>
+          <t>limfadenopatiya</t>
+        </is>
+      </c>
+      <c r="F251" s="23" t="n"/>
+      <c r="G251" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H251" s="24" t="n"/>
+      <c r="I251" s="24" t="n"/>
+      <c r="J251" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="22" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C252" s="23" t="inlineStr">
+        <is>
+          <t>enlarged lymph node</t>
+        </is>
+      </c>
+      <c r="D252" s="23" t="inlineStr">
+        <is>
+          <t>enlarged lymph nodes</t>
+        </is>
+      </c>
+      <c r="E252" s="23" t="inlineStr">
+        <is>
+          <t>kattalashgan limfa tuguni</t>
+        </is>
+      </c>
+      <c r="F252" s="23" t="n"/>
+      <c r="G252" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H252" s="24" t="n"/>
+      <c r="I252" s="24" t="n"/>
+      <c r="J252" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="22" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="23" t="inlineStr">
+        <is>
+          <t>Qorin bo'shlig'i a'zolari</t>
+        </is>
+      </c>
+      <c r="C253" s="23" t="inlineStr">
+        <is>
+          <t>appendicitis</t>
+        </is>
+      </c>
+      <c r="D253" s="23" t="n"/>
+      <c r="E253" s="23" t="inlineStr">
+        <is>
+          <t>appenditsit</t>
+        </is>
+      </c>
+      <c r="F253" s="23" t="n"/>
+      <c r="G253" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H253" s="24" t="n"/>
+      <c r="I253" s="24" t="n"/>
+      <c r="J253" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="22" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="23" t="inlineStr">
+        <is>
+          <t>Qorin bo'shlig'i a'zolari</t>
+        </is>
+      </c>
+      <c r="C254" s="23" t="inlineStr">
+        <is>
+          <t>acute appendicitis</t>
+        </is>
+      </c>
+      <c r="D254" s="23" t="n"/>
+      <c r="E254" s="23" t="inlineStr">
+        <is>
+          <t>o‘tkir appenditsit</t>
+        </is>
+      </c>
+      <c r="F254" s="23" t="n"/>
+      <c r="G254" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H254" s="24" t="n"/>
+      <c r="I254" s="24" t="n"/>
+      <c r="J254" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="22" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C255" s="23" t="inlineStr">
+        <is>
+          <t>complex mass</t>
+        </is>
+      </c>
+      <c r="D255" s="23" t="inlineStr">
+        <is>
+          <t>complex masses</t>
+        </is>
+      </c>
+      <c r="E255" s="23" t="inlineStr">
+        <is>
+          <t>murakkab tuzilishli hosila</t>
+        </is>
+      </c>
+      <c r="F255" s="23" t="n"/>
+      <c r="G255" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H255" s="24" t="n"/>
+      <c r="I255" s="24" t="n"/>
+      <c r="J255" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="22" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C256" s="23" t="inlineStr">
+        <is>
+          <t>cystic mass</t>
+        </is>
+      </c>
+      <c r="D256" s="23" t="inlineStr">
+        <is>
+          <t>cystic masses</t>
+        </is>
+      </c>
+      <c r="E256" s="23" t="inlineStr">
+        <is>
+          <t>kistasimon hosila</t>
+        </is>
+      </c>
+      <c r="F256" s="23" t="n"/>
+      <c r="G256" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H256" s="24" t="n"/>
+      <c r="I256" s="24" t="n"/>
+      <c r="J256" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="22" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C257" s="23" t="inlineStr">
+        <is>
+          <t>hemorrhage</t>
+        </is>
+      </c>
+      <c r="D257" s="23" t="inlineStr">
+        <is>
+          <t>haemorrhage</t>
+        </is>
+      </c>
+      <c r="E257" s="23" t="inlineStr">
+        <is>
+          <t>qon quyilishi</t>
+        </is>
+      </c>
+      <c r="F257" s="23" t="n"/>
+      <c r="G257" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H257" s="24" t="n"/>
+      <c r="I257" s="24" t="n"/>
+      <c r="J257" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="22" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="23" t="inlineStr">
+        <is>
+          <t>Neyrosonografiya</t>
+        </is>
+      </c>
+      <c r="C258" s="23" t="inlineStr">
+        <is>
+          <t>germinal matrix hemorrhage</t>
+        </is>
+      </c>
+      <c r="D258" s="23" t="inlineStr">
+        <is>
+          <t>germinal matrix haemorrhage; GMH</t>
+        </is>
+      </c>
+      <c r="E258" s="23" t="inlineStr">
+        <is>
+          <t>germinal matriksga qon quyilishi</t>
+        </is>
+      </c>
+      <c r="F258" s="23" t="n"/>
+      <c r="G258" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H258" s="24" t="n"/>
+      <c r="I258" s="24" t="n"/>
+      <c r="J258" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="22" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="23" t="inlineStr">
+        <is>
+          <t>Neyrosonografiya</t>
+        </is>
+      </c>
+      <c r="C259" s="23" t="inlineStr">
+        <is>
+          <t>germinal matrix-intraventricular hemorrhage</t>
+        </is>
+      </c>
+      <c r="D259" s="23" t="inlineStr">
+        <is>
+          <t>germinal matrix intraventricular hemorrhage; germinal matrix-intraventricular haemorrhage; GM-IVH</t>
+        </is>
+      </c>
+      <c r="E259" s="23" t="inlineStr">
+        <is>
+          <t>germinal matriks va qorinchalar ichiga qon quyilishi (GM-IVH)</t>
+        </is>
+      </c>
+      <c r="F259" s="23" t="n"/>
+      <c r="G259" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H259" s="24" t="n"/>
+      <c r="I259" s="24" t="n"/>
+      <c r="J259" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="22" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" s="23" t="inlineStr">
+        <is>
+          <t>Neyrosonografiya</t>
+        </is>
+      </c>
+      <c r="C260" s="23" t="inlineStr">
+        <is>
+          <t>fontanelle</t>
+        </is>
+      </c>
+      <c r="D260" s="23" t="inlineStr">
+        <is>
+          <t>fontanel</t>
+        </is>
+      </c>
+      <c r="E260" s="23" t="inlineStr">
+        <is>
+          <t>liqildoq</t>
+        </is>
+      </c>
+      <c r="F260" s="23" t="n"/>
+      <c r="G260" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H260" s="24" t="n"/>
+      <c r="I260" s="24" t="n"/>
+      <c r="J260" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="22" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" s="23" t="inlineStr">
+        <is>
+          <t>Neyrosonografiya</t>
+        </is>
+      </c>
+      <c r="C261" s="23" t="inlineStr">
+        <is>
+          <t>posterior fontanelle</t>
+        </is>
+      </c>
+      <c r="D261" s="23" t="inlineStr">
+        <is>
+          <t>posterior fontanel</t>
+        </is>
+      </c>
+      <c r="E261" s="23" t="inlineStr">
+        <is>
+          <t>orqa liqildoq</t>
+        </is>
+      </c>
+      <c r="F261" s="23" t="n"/>
+      <c r="G261" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H261" s="24" t="n"/>
+      <c r="I261" s="24" t="n"/>
+      <c r="J261" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="22" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C262" s="23" t="inlineStr">
+        <is>
+          <t>septum</t>
+        </is>
+      </c>
+      <c r="D262" s="23" t="inlineStr">
+        <is>
+          <t>septa</t>
+        </is>
+      </c>
+      <c r="E262" s="23" t="inlineStr">
+        <is>
+          <t>to‘siq</t>
+        </is>
+      </c>
+      <c r="F262" s="23" t="n"/>
+      <c r="G262" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H262" s="24" t="n"/>
+      <c r="I262" s="24" t="n"/>
+      <c r="J262" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="22" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="23" t="inlineStr">
+        <is>
+          <t>Exokardiografiya</t>
+        </is>
+      </c>
+      <c r="C263" s="23" t="inlineStr">
+        <is>
+          <t>interatrial septum</t>
+        </is>
+      </c>
+      <c r="D263" s="23" t="n"/>
+      <c r="E263" s="23" t="inlineStr">
+        <is>
+          <t>bo‘lmachalararo to‘siq</t>
+        </is>
+      </c>
+      <c r="F263" s="23" t="n"/>
+      <c r="G263" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H263" s="24" t="n"/>
+      <c r="I263" s="24" t="n"/>
+      <c r="J263" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="22" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C264" s="23" t="inlineStr">
+        <is>
+          <t>septation</t>
+        </is>
+      </c>
+      <c r="D264" s="23" t="inlineStr">
+        <is>
+          <t>septations; cyst septation; cyst septations</t>
+        </is>
+      </c>
+      <c r="E264" s="23" t="inlineStr">
+        <is>
+          <t>kista ichidagi to‘siq (septa)</t>
+        </is>
+      </c>
+      <c r="F264" s="23" t="n"/>
+      <c r="G264" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H264" s="24" t="n"/>
+      <c r="I264" s="24" t="n"/>
+      <c r="J264" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="22" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="23" t="inlineStr">
+        <is>
+          <t>Tasvir va exogenlik</t>
+        </is>
+      </c>
+      <c r="C265" s="23" t="inlineStr">
+        <is>
+          <t>echogenic</t>
+        </is>
+      </c>
+      <c r="D265" s="23" t="n"/>
+      <c r="E265" s="23" t="inlineStr">
+        <is>
+          <t>exogen</t>
+        </is>
+      </c>
+      <c r="F265" s="23" t="n"/>
+      <c r="G265" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H265" s="24" t="n"/>
+      <c r="I265" s="24" t="n"/>
+      <c r="J265" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="22" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" s="23" t="inlineStr">
+        <is>
+          <t>Artefakt va fizika</t>
+        </is>
+      </c>
+      <c r="C266" s="23" t="inlineStr">
+        <is>
+          <t>spatial resolution</t>
+        </is>
+      </c>
+      <c r="D266" s="23" t="n"/>
+      <c r="E266" s="23" t="inlineStr">
+        <is>
+          <t>fazoviy ajrata olish qobiliyati (fazoviy rezolyutsiya)</t>
+        </is>
+      </c>
+      <c r="F266" s="23" t="n"/>
+      <c r="G266" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H266" s="24" t="n"/>
+      <c r="I266" s="24" t="n"/>
+      <c r="J266" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="22" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" s="23" t="inlineStr">
+        <is>
+          <t>Artefakt va fizika</t>
+        </is>
+      </c>
+      <c r="C267" s="23" t="inlineStr">
+        <is>
+          <t>high frequency</t>
+        </is>
+      </c>
+      <c r="D267" s="23" t="n"/>
+      <c r="E267" s="23" t="inlineStr">
+        <is>
+          <t>yuqori chastota</t>
+        </is>
+      </c>
+      <c r="F267" s="23" t="n"/>
+      <c r="G267" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H267" s="24" t="n"/>
+      <c r="I267" s="24" t="n"/>
+      <c r="J267" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="22" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C268" s="23" t="inlineStr">
+        <is>
+          <t>benign tumor</t>
+        </is>
+      </c>
+      <c r="D268" s="23" t="inlineStr">
+        <is>
+          <t>benign tumour</t>
+        </is>
+      </c>
+      <c r="E268" s="23" t="inlineStr">
+        <is>
+          <t>yaxshi sifatli o‘sma</t>
+        </is>
+      </c>
+      <c r="F268" s="23" t="n"/>
+      <c r="G268" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H268" s="24" t="n"/>
+      <c r="I268" s="24" t="n"/>
+      <c r="J268" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="22" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" s="23" t="inlineStr">
+        <is>
+          <t>Umumiy patologiya</t>
+        </is>
+      </c>
+      <c r="C269" s="23" t="inlineStr">
+        <is>
+          <t>malignant tumor</t>
+        </is>
+      </c>
+      <c r="D269" s="23" t="inlineStr">
+        <is>
+          <t>malignant tumour</t>
+        </is>
+      </c>
+      <c r="E269" s="23" t="inlineStr">
+        <is>
+          <t>yomon sifatli o‘sma</t>
+        </is>
+      </c>
+      <c r="F269" s="23" t="n"/>
+      <c r="G269" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H269" s="24" t="n"/>
+      <c r="I269" s="24" t="n"/>
+      <c r="J269" s="24" t="inlineStr">
         <is>
           <t>Yo'q</t>
         </is>

--- a/docs/glossary/UZI_atamalari_tekshirilgan.xlsx
+++ b/docs/glossary/UZI_atamalari_tekshirilgan.xlsx
@@ -807,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J269"/>
+  <dimension ref="A1:J270"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="12" min="1" max="1"/>
@@ -11469,6 +11469,44 @@
       <c r="H269" s="24" t="n"/>
       <c r="I269" s="24" t="n"/>
       <c r="J269" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="22" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" s="23" t="inlineStr">
+        <is>
+          <t>Qorin bo'shlig'i a'zolari</t>
+        </is>
+      </c>
+      <c r="C270" s="23" t="inlineStr">
+        <is>
+          <t>lymphatic vessel</t>
+        </is>
+      </c>
+      <c r="D270" s="23" t="inlineStr">
+        <is>
+          <t>lymphatic vessels; lymph vessel; lymph vessels</t>
+        </is>
+      </c>
+      <c r="E270" s="23" t="inlineStr">
+        <is>
+          <t>limfa tomiri</t>
+        </is>
+      </c>
+      <c r="F270" s="23" t="n"/>
+      <c r="G270" s="24" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="H270" s="24" t="n"/>
+      <c r="I270" s="24" t="n"/>
+      <c r="J270" s="24" t="inlineStr">
         <is>
           <t>Yo'q</t>
         </is>

--- a/docs/glossary/UZI_atamalari_tekshirilgan.xlsx
+++ b/docs/glossary/UZI_atamalari_tekshirilgan.xlsx
@@ -807,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J270"/>
+  <dimension ref="A1:J274"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="12" min="1" max="1"/>
@@ -11507,6 +11507,151 @@
       <c r="H270" s="24" t="n"/>
       <c r="I270" s="24" t="n"/>
       <c r="J270" s="24" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Tasvir va exogenlik</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>plane</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>planes; scan plane; scanning plane; imaging plane; image plane; section plane</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>kesim (tekislik)</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Ultratovush kesimi (skanerlash tekisligi). 'Samolyot' deb tarjima qilinmaydi.</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Tasvir va exogenlik</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>sagittal plane</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>sagittal section; sagittal view; sagittal planes</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>sagittal kesim</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Tasvir va exogenlik</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>transverse plane</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>transverse view; axial plane; transverse planes</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>ko‘ndalang kesim</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Yo'q</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Tasvir va exogenlik</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>coronal plane</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>coronal section; coronal view; coronal planes</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>frontal (koronar) kesim</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
         <is>
           <t>Yo'q</t>
         </is>

--- a/docs/glossary/UZI_atamalari_tekshirilgan.xlsx
+++ b/docs/glossary/UZI_atamalari_tekshirilgan.xlsx
@@ -11513,145 +11513,145 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="n">
+      <c r="A271" s="12" t="n">
         <v>270</v>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B271" s="12" t="inlineStr">
         <is>
           <t>Tasvir va exogenlik</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
+      <c r="C271" s="12" t="inlineStr">
         <is>
           <t>plane</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
+      <c r="D271" s="12" t="inlineStr">
         <is>
           <t>planes; scan plane; scanning plane; imaging plane; image plane; section plane</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
+      <c r="E271" s="12" t="inlineStr">
         <is>
           <t>kesim (tekislik)</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
+      <c r="F271" s="12" t="inlineStr">
         <is>
           <t>Ultratovush kesimi (skanerlash tekisligi). 'Samolyot' deb tarjima qilinmaydi.</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
+      <c r="G271" s="12" t="inlineStr">
         <is>
           <t>Yangi</t>
         </is>
       </c>
-      <c r="J271" t="inlineStr">
+      <c r="J271" s="12" t="inlineStr">
         <is>
           <t>Yo'q</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="n">
+      <c r="A272" s="12" t="n">
         <v>271</v>
       </c>
-      <c r="B272" t="inlineStr">
+      <c r="B272" s="12" t="inlineStr">
         <is>
           <t>Tasvir va exogenlik</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
+      <c r="C272" s="12" t="inlineStr">
         <is>
           <t>sagittal plane</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
+      <c r="D272" s="12" t="inlineStr">
         <is>
           <t>sagittal section; sagittal view; sagittal planes</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
+      <c r="E272" s="12" t="inlineStr">
         <is>
           <t>sagittal kesim</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr">
+      <c r="G272" s="12" t="inlineStr">
         <is>
           <t>Yangi</t>
         </is>
       </c>
-      <c r="J272" t="inlineStr">
+      <c r="J272" s="12" t="inlineStr">
         <is>
           <t>Yo'q</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="n">
+      <c r="A273" s="12" t="n">
         <v>272</v>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B273" s="12" t="inlineStr">
         <is>
           <t>Tasvir va exogenlik</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
+      <c r="C273" s="12" t="inlineStr">
         <is>
           <t>transverse plane</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
+      <c r="D273" s="12" t="inlineStr">
         <is>
           <t>transverse view; axial plane; transverse planes</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
+      <c r="E273" s="12" t="inlineStr">
         <is>
           <t>ko‘ndalang kesim</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
+      <c r="G273" s="12" t="inlineStr">
         <is>
           <t>Yangi</t>
         </is>
       </c>
-      <c r="J273" t="inlineStr">
+      <c r="J273" s="12" t="inlineStr">
         <is>
           <t>Yo'q</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="n">
+      <c r="A274" s="12" t="n">
         <v>273</v>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B274" s="12" t="inlineStr">
         <is>
           <t>Tasvir va exogenlik</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
+      <c r="C274" s="12" t="inlineStr">
         <is>
           <t>coronal plane</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
+      <c r="D274" s="12" t="inlineStr">
         <is>
           <t>coronal section; coronal view; coronal planes</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>frontal (koronar) kesim</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
+      <c r="E274" s="12" t="inlineStr">
+        <is>
+          <t>koronal kesim</t>
+        </is>
+      </c>
+      <c r="G274" s="12" t="inlineStr">
         <is>
           <t>Yangi</t>
         </is>
       </c>
-      <c r="J274" t="inlineStr">
+      <c r="J274" s="12" t="inlineStr">
         <is>
           <t>Yo'q</t>
         </is>
